--- a/Supplementary_Data_2.xlsx
+++ b/Supplementary_Data_2.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_Raw_and_Fit" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_Fit_Parameters" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_Bootstrap_CI" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_Kappa_Scan" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_FixedKappa_Test" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_Bootstrap_Summary" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="1_Raw_and_Fit" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2_Fit_Parameters" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="3_Bootstrap_CI" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="4_Kappa_Scan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="5_FixedKappa_Test" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="6_Bootstrap_Summary" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,10 +483,10 @@
         <v>0.7262999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7191683320015717</v>
+        <v>0.7191670556562703</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007131667998428237</v>
+        <v>0.007132944343729686</v>
       </c>
     </row>
     <row r="3">
@@ -507,10 +507,10 @@
         <v>0.6667</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6571005473198468</v>
+        <v>0.6571000258383516</v>
       </c>
       <c r="F3" t="n">
-        <v>0.009599452680153164</v>
+        <v>0.009599974161648372</v>
       </c>
     </row>
     <row r="4">
@@ -524,17 +524,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.6730</t>
+          <t>0.6731</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.5909</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6048943177850381</v>
+        <v>0.6048942391424662</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.01399431778503812</v>
+        <v>-0.01399423914246622</v>
       </c>
     </row>
     <row r="5">
@@ -555,10 +555,10 @@
         <v>0.5556</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5603712641006603</v>
+        <v>0.5603714429957997</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.004771264100660311</v>
+        <v>-0.00477144299579968</v>
       </c>
     </row>
     <row r="6">
@@ -572,17 +572,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.6826</t>
+          <t>1.6827</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.4694</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4884666144411774</v>
+        <v>0.4884670140063888</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.01906661444117747</v>
+        <v>-0.01906701400638883</v>
       </c>
     </row>
     <row r="7">
@@ -596,17 +596,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.3652</t>
+          <t>3.3653</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.3942</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3698258893887715</v>
+        <v>0.3698262698100431</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02437411061122846</v>
+        <v>0.02437373018995687</v>
       </c>
     </row>
     <row r="9">
@@ -619,7 +619,7 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>0.982504057786949</v>
+        <v>0.9825037339685829</v>
       </c>
       <c r="F9" t="inlineStr"/>
     </row>
@@ -633,7 +633,7 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
-        <v>2.076388959353378</v>
+        <v>2.076365987956136</v>
       </c>
       <c r="F10" t="inlineStr"/>
     </row>
@@ -647,7 +647,7 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>-0.007131667998428237</v>
+        <v>-0.007132944343729686</v>
       </c>
       <c r="F11" t="inlineStr"/>
     </row>
@@ -694,10 +694,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>697.1815424346468</v>
+        <v>620.3594384762689</v>
       </c>
       <c r="C2" t="n">
-        <v>1219833.762560507</v>
+        <v>1942237.239549272</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.365178640341263</v>
+        <v>3.365335958106503</v>
       </c>
       <c r="C3" t="n">
-        <v>2.769920198890599</v>
+        <v>5.470075279575834</v>
       </c>
       <c r="D3" t="inlineStr"/>
     </row>
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.5618835129766</v>
+        <v>2.561995067525961</v>
       </c>
       <c r="C4" t="n">
-        <v>1.742834629345366</v>
+        <v>3.57145501499949</v>
       </c>
       <c r="D4" t="inlineStr"/>
     </row>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.982504057786949</v>
+        <v>0.9825037339685829</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01482817771408041</v>
+        <v>0.01482831493487153</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.076388959353378</v>
+        <v>2.076365987956136</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -883,16 +883,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>697.1815424346468</v>
+        <v>620.3594384762689</v>
       </c>
       <c r="C2" t="n">
-        <v>1.248602296381743</v>
+        <v>0.1164677691622355</v>
       </c>
       <c r="D2" t="n">
-        <v>5494.027815819306</v>
+        <v>4016.665455722818</v>
       </c>
       <c r="E2" t="n">
-        <v>3.643466724554152</v>
+        <v>4.537659904238419</v>
       </c>
     </row>
     <row r="3">
@@ -902,13 +902,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.365178640341263</v>
+        <v>3.365335958106503</v>
       </c>
       <c r="C3" t="n">
-        <v>2.211022129160111</v>
+        <v>2.21028630815452</v>
       </c>
       <c r="D3" t="n">
-        <v>5.446245155835491</v>
+        <v>16.46219727083571</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.5618835129766</v>
+        <v>2.561995067525961</v>
       </c>
       <c r="C4" t="n">
-        <v>2.069264419193585</v>
+        <v>2.068870873497739</v>
       </c>
       <c r="D4" t="n">
-        <v>3.300521099191581</v>
+        <v>8.890662491976421</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>κ CI spans 3.6 orders of magnitude; reported as κ ≥ 1.25</t>
+          <t>κ CI spans 4.5 orders of magnitude; reported as κ ≥ 0.12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -994,13 +994,13 @@
         <v>0.001</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7845651922919695</v>
+        <v>0.7845651923115642</v>
       </c>
       <c r="C2" t="n">
-        <v>1433.669012746175</v>
+        <v>1433.669246982661</v>
       </c>
       <c r="D2" t="n">
-        <v>670.6366574978288</v>
+        <v>670.6366859521637</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1013,13 +1013,13 @@
         <v>0.01</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8645441597353984</v>
+        <v>0.8645441597351768</v>
       </c>
       <c r="C3" t="n">
-        <v>142.9375139949267</v>
+        <v>142.9375115024475</v>
       </c>
       <c r="D3" t="n">
-        <v>70.72720169418362</v>
+        <v>70.72720186507073</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1032,13 +1032,13 @@
         <v>0.1</v>
       </c>
       <c r="B4" t="n">
-        <v>0.959557654365801</v>
+        <v>0.9595576543658344</v>
       </c>
       <c r="C4" t="n">
-        <v>15.64217638973279</v>
+        <v>15.64217655263832</v>
       </c>
       <c r="D4" t="n">
-        <v>9.520655980135688</v>
+        <v>9.520656026321555</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1051,13 +1051,13 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9805529966488032</v>
+        <v>0.9805529966488051</v>
       </c>
       <c r="C5" t="n">
-        <v>4.472841284076064</v>
+        <v>4.472841434705499</v>
       </c>
       <c r="D5" t="n">
-        <v>3.263946866330599</v>
+        <v>3.263946911704474</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1070,13 +1070,13 @@
         <v>10</v>
       </c>
       <c r="B6" t="n">
-        <v>0.982322896884771</v>
+        <v>0.9823228968847157</v>
       </c>
       <c r="C6" t="n">
-        <v>3.472382213886906</v>
+        <v>3.472380936077815</v>
       </c>
       <c r="D6" t="n">
-        <v>2.631310576419495</v>
+        <v>2.631310102812652</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1089,13 +1089,13 @@
         <v>100</v>
       </c>
       <c r="B7" t="n">
-        <v>0.9824884303369781</v>
+        <v>0.982488430336756</v>
       </c>
       <c r="C7" t="n">
-        <v>3.374452229525813</v>
+        <v>3.374448163788455</v>
       </c>
       <c r="D7" t="n">
-        <v>2.567909126729743</v>
+        <v>2.567907862355811</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1108,13 +1108,13 @@
         <v>1000</v>
       </c>
       <c r="B8" t="n">
-        <v>0.9825048495134774</v>
+        <v>0.9825048496388544</v>
       </c>
       <c r="C8" t="n">
-        <v>3.364760276961306</v>
+        <v>3.364671812410771</v>
       </c>
       <c r="D8" t="n">
-        <v>2.561595355373473</v>
+        <v>2.56156409781555</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1127,13 +1127,13 @@
         <v>10000</v>
       </c>
       <c r="B9" t="n">
-        <v>0.9825064900836757</v>
+        <v>0.9825064890024684</v>
       </c>
       <c r="C9" t="n">
-        <v>3.363627461370567</v>
+        <v>3.363463502422903</v>
       </c>
       <c r="D9" t="n">
-        <v>2.560903644601107</v>
+        <v>2.560844104413405</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1207,11 +1207,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>697.2</t>
+          <t>620.4</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.982504057786949</v>
+        <v>0.9825037339685829</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1227,10 +1227,10 @@
         <v>0.1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.959557654365801</v>
+        <v>0.9595576543658344</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.02294640342114806</v>
+        <v>-0.02294607960274853</v>
       </c>
     </row>
     <row r="4">
@@ -1243,10 +1243,10 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9805529966488032</v>
+        <v>0.9805529966488051</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.001951061138145804</v>
+        <v>-0.001950737319777796</v>
       </c>
     </row>
   </sheetData>
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1052.39913565383</v>
+        <v>794.4657113553761</v>
       </c>
       <c r="C3" t="n">
-        <v>3.36434393509664</v>
+        <v>3.363929198252801</v>
       </c>
       <c r="D3" t="n">
-        <v>2.58346136055678</v>
+        <v>2.583081071798213</v>
       </c>
     </row>
     <row r="4">
@@ -1324,13 +1324,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1639.357081005456</v>
+        <v>1061.429976128172</v>
       </c>
       <c r="C4" t="n">
-        <v>3.759993047938654</v>
+        <v>4.341907230960193</v>
       </c>
       <c r="D4" t="n">
-        <v>2.721725979170995</v>
+        <v>2.979249779180651</v>
       </c>
     </row>
     <row r="5">
@@ -1340,13 +1340,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2162.871803739974</v>
+        <v>916.1903675881024</v>
       </c>
       <c r="C5" t="n">
-        <v>3.487996118886838</v>
+        <v>5.529602792467628</v>
       </c>
       <c r="D5" t="n">
-        <v>1.588420352969517</v>
+        <v>2.344429893624975</v>
       </c>
     </row>
     <row r="6">
@@ -1356,13 +1356,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01769064660201317</v>
+        <v>0.0176906466020088</v>
       </c>
       <c r="C6" t="n">
-        <v>1.358252374819121</v>
+        <v>1.179167974658647</v>
       </c>
       <c r="D6" t="n">
-        <v>1.609448873563088</v>
+        <v>1.436747470951438</v>
       </c>
     </row>
     <row r="7">
@@ -1372,13 +1372,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>28696.27230916805</v>
+        <v>7374.374580712363</v>
       </c>
       <c r="C7" t="n">
-        <v>76.55976903335618</v>
+        <v>76.55976903337498</v>
       </c>
       <c r="D7" t="n">
-        <v>36.99347429871575</v>
+        <v>36.9934742987244</v>
       </c>
     </row>
   </sheetData>
